--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sodomall-my.sharepoint.com/personal/jinyeong617_sodomall_com/Documents/당근/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{9D1964EF-D87C-40DB-87AD-82C7614BA687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74A54C42-5118-4989-8C60-5AE1EA5AE409}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{9D1964EF-D87C-40DB-87AD-82C7614BA687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D255B4FD-CFCC-4DB6-89E4-6549BDF8CE15}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77D1A517-C785-428C-9931-F09A076C124D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="235">
   <si>
     <t>상품</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9060,6 +9060,2146 @@
         <charset val="129"/>
       </rPr>
       <t>종세트</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쭈꾸미</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>볶음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (300g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메디앤서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>트리플</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>샷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>콜라겐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마스크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곽</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이블 무선 써큘레이터 1개</t>
+  </si>
+  <si>
+    <t>한우 ''견과'' 육포 1봉 (30g)</t>
+  </si>
+  <si>
+    <t>한우 육포 1봉 (30g)</t>
+  </si>
+  <si>
+    <t>로투스 비스코프 비스켓 (93g*3팩)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>직화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갈비맛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>핫바</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (65g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명장 김치찌개&amp;찜 1팩 (250g)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국내산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한돈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>막고기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (300g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>망고향</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>블랙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스윗마토</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (500g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[깜짝공구] 손질 통낙지 1팩(280g)</t>
+  </si>
+  <si>
+    <t>도루코 애쉬블루 IH 프라이팬(24cm)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도루코</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>애쉬블루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> IH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프라이팬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(20cm)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비오셀라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>히알루로닉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>케어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세트</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인천시장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어묵쫄우동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(315g*2)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미스타셰프 버섯뚝배기불고기 1팩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꼬소명가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참기름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>' 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (350ml)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꼬소명가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들기름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>' 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (350ml)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고추장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보리장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (300g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명가꽈배기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참깨맛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (500g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명가꽈배기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흑당맛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (500g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>망고바</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(50g*10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>폴메디슨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>케어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>크림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세트</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유황먹여 키운 복 삼계탕 1팩(1kg)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이싱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쿨링타올</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (40g*5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕만두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (750g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김치 왕만두 1봉 (750g)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캡슐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세탁조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클리너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>퍼퓸앰플</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건조기시트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실내건조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>액체세제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2.8L</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깐새우장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(400g/10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양파듬뿍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삼일카레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(210g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소프트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슬라이드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치간칫솔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(56</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅콩샌드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (400g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더마콜라겐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시그니처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교동 황태어글탕 1팩 (600g)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문은희</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>창난젓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (400g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>옥자씨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곤약쫀드기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(25g*15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알쿠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탈취제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (350g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국내산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아삭이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고추</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 150g)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -9068,7 +11208,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9215,7 +11355,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF2A3038"/>
-      <name val="맑은 고딕"/>
+      <name val="Segoe UI"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -9223,15 +11363,21 @@
       <sz val="11"/>
       <color rgb="FF2A3038"/>
       <name val="Segoe UI"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF2A3038"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A3038"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="7">
@@ -9301,7 +11447,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9368,22 +11514,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9408,6 +11551,10 @@
 </file>
 
 <file path=xl/persons/person0.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person1.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -9708,7 +11855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC37B53-3382-4F2F-9306-BB57C25FEA41}">
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D222"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.375" customWidth="1"/>
@@ -11636,13 +13783,13 @@
       </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="22">
+      <c r="A138" s="9">
         <v>20260513</v>
       </c>
-      <c r="B138" s="23" t="s">
+      <c r="B138" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C138" s="22" t="s">
+      <c r="C138" s="9" t="s">
         <v>91</v>
       </c>
       <c r="D138" s="11">
@@ -11650,10 +13797,10 @@
       </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="22">
+      <c r="A139" s="9">
         <v>20260513</v>
       </c>
-      <c r="B139" s="24" t="s">
+      <c r="B139" s="22" t="s">
         <v>150</v>
       </c>
       <c r="C139" s="9" t="s">
@@ -11664,10 +13811,10 @@
       </c>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="22">
+      <c r="A140" s="9">
         <v>20260513</v>
       </c>
-      <c r="B140" s="24" t="s">
+      <c r="B140" s="22" t="s">
         <v>151</v>
       </c>
       <c r="C140" s="13" t="s">
@@ -11678,10 +13825,10 @@
       </c>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="22">
+      <c r="A141" s="9">
         <v>20260513</v>
       </c>
-      <c r="B141" s="25" t="s">
+      <c r="B141" s="23" t="s">
         <v>152</v>
       </c>
       <c r="C141" s="13" t="s">
@@ -11692,10 +13839,10 @@
       </c>
     </row>
     <row r="142" spans="1:4">
-      <c r="A142" s="22">
+      <c r="A142" s="9">
         <v>20260513</v>
       </c>
-      <c r="B142" s="24" t="s">
+      <c r="B142" s="22" t="s">
         <v>153</v>
       </c>
       <c r="C142" s="13" t="s">
@@ -11706,10 +13853,10 @@
       </c>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="22">
+      <c r="A143" s="9">
         <v>20260514</v>
       </c>
-      <c r="B143" s="24" t="s">
+      <c r="B143" s="22" t="s">
         <v>154</v>
       </c>
       <c r="C143" s="13" t="s">
@@ -11720,10 +13867,10 @@
       </c>
     </row>
     <row r="144" spans="1:4">
-      <c r="A144" s="22">
+      <c r="A144" s="9">
         <v>20260514</v>
       </c>
-      <c r="B144" s="25" t="s">
+      <c r="B144" s="23" t="s">
         <v>155</v>
       </c>
       <c r="C144" s="13" t="s">
@@ -11734,10 +13881,10 @@
       </c>
     </row>
     <row r="145" spans="1:4">
-      <c r="A145" s="22">
+      <c r="A145" s="9">
         <v>20260514</v>
       </c>
-      <c r="B145" s="24" t="s">
+      <c r="B145" s="22" t="s">
         <v>156</v>
       </c>
       <c r="C145" s="13" t="s">
@@ -11748,10 +13895,10 @@
       </c>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="22">
+      <c r="A146" s="9">
         <v>20260514</v>
       </c>
-      <c r="B146" s="24" t="s">
+      <c r="B146" s="22" t="s">
         <v>157</v>
       </c>
       <c r="C146" s="13" t="s">
@@ -11762,10 +13909,10 @@
       </c>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="22">
+      <c r="A147" s="9">
         <v>20260515</v>
       </c>
-      <c r="B147" s="26" t="s">
+      <c r="B147" s="22" t="s">
         <v>158</v>
       </c>
       <c r="C147" s="13" t="s">
@@ -11776,10 +13923,10 @@
       </c>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="22">
+      <c r="A148" s="9">
         <v>20260515</v>
       </c>
-      <c r="B148" s="24" t="s">
+      <c r="B148" s="22" t="s">
         <v>159</v>
       </c>
       <c r="C148" s="13" t="s">
@@ -11790,10 +13937,10 @@
       </c>
     </row>
     <row r="149" spans="1:4">
-      <c r="A149" s="22">
+      <c r="A149" s="9">
         <v>20260515</v>
       </c>
-      <c r="B149" s="24" t="s">
+      <c r="B149" s="22" t="s">
         <v>160</v>
       </c>
       <c r="C149" s="13" t="s">
@@ -11804,10 +13951,10 @@
       </c>
     </row>
     <row r="150" spans="1:4">
-      <c r="A150" s="22">
+      <c r="A150" s="9">
         <v>20260515</v>
       </c>
-      <c r="B150" s="25" t="s">
+      <c r="B150" s="23" t="s">
         <v>161</v>
       </c>
       <c r="C150" s="13" t="s">
@@ -11818,10 +13965,10 @@
       </c>
     </row>
     <row r="151" spans="1:4">
-      <c r="A151" s="22">
+      <c r="A151" s="9">
         <v>20260515</v>
       </c>
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="23" t="s">
         <v>162</v>
       </c>
       <c r="C151" s="13" t="s">
@@ -11832,10 +13979,10 @@
       </c>
     </row>
     <row r="152" spans="1:4">
-      <c r="A152" s="22">
+      <c r="A152" s="9">
         <v>20260515</v>
       </c>
-      <c r="B152" s="27" t="s">
+      <c r="B152" s="23" t="s">
         <v>163</v>
       </c>
       <c r="C152" s="13" t="s">
@@ -11846,10 +13993,10 @@
       </c>
     </row>
     <row r="153" spans="1:4">
-      <c r="A153" s="22">
+      <c r="A153" s="9">
         <v>20260515</v>
       </c>
-      <c r="B153" s="27" t="s">
+      <c r="B153" s="23" t="s">
         <v>164</v>
       </c>
       <c r="C153" s="13" t="s">
@@ -11860,10 +14007,10 @@
       </c>
     </row>
     <row r="154" spans="1:4">
-      <c r="A154" s="22">
+      <c r="A154" s="9">
         <v>20260515</v>
       </c>
-      <c r="B154" s="27" t="s">
+      <c r="B154" s="23" t="s">
         <v>165</v>
       </c>
       <c r="C154" s="13" t="s">
@@ -11874,10 +14021,10 @@
       </c>
     </row>
     <row r="155" spans="1:4">
-      <c r="A155" s="22">
+      <c r="A155" s="9">
         <v>20260515</v>
       </c>
-      <c r="B155" s="27" t="s">
+      <c r="B155" s="23" t="s">
         <v>166</v>
       </c>
       <c r="C155" s="13" t="s">
@@ -11888,10 +14035,10 @@
       </c>
     </row>
     <row r="156" spans="1:4">
-      <c r="A156" s="22">
+      <c r="A156" s="9">
         <v>20260515</v>
       </c>
-      <c r="B156" s="27" t="s">
+      <c r="B156" s="23" t="s">
         <v>167</v>
       </c>
       <c r="C156" s="13" t="s">
@@ -11902,10 +14049,10 @@
       </c>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="22">
+      <c r="A157" s="9">
         <v>20260515</v>
       </c>
-      <c r="B157" s="27" t="s">
+      <c r="B157" s="23" t="s">
         <v>168</v>
       </c>
       <c r="C157" s="13" t="s">
@@ -11916,10 +14063,10 @@
       </c>
     </row>
     <row r="158" spans="1:4">
-      <c r="A158" s="22">
+      <c r="A158" s="9">
         <v>20260515</v>
       </c>
-      <c r="B158" s="27" t="s">
+      <c r="B158" s="23" t="s">
         <v>169</v>
       </c>
       <c r="C158" s="13" t="s">
@@ -11930,10 +14077,10 @@
       </c>
     </row>
     <row r="159" spans="1:4">
-      <c r="A159" s="22">
+      <c r="A159" s="9">
         <v>20260516</v>
       </c>
-      <c r="B159" s="25" t="s">
+      <c r="B159" s="23" t="s">
         <v>170</v>
       </c>
       <c r="C159" s="13" t="s">
@@ -11944,10 +14091,10 @@
       </c>
     </row>
     <row r="160" spans="1:4">
-      <c r="A160" s="22">
+      <c r="A160" s="9">
         <v>20260516</v>
       </c>
-      <c r="B160" s="24" t="s">
+      <c r="B160" s="22" t="s">
         <v>171</v>
       </c>
       <c r="C160" s="13" t="s">
@@ -11958,10 +14105,10 @@
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="22">
+      <c r="A161" s="9">
         <v>20260516</v>
       </c>
-      <c r="B161" s="26" t="s">
+      <c r="B161" s="22" t="s">
         <v>172</v>
       </c>
       <c r="C161" s="13" t="s">
@@ -11972,10 +14119,10 @@
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="22">
+      <c r="A162" s="9">
         <v>20260516</v>
       </c>
-      <c r="B162" s="26" t="s">
+      <c r="B162" s="22" t="s">
         <v>173</v>
       </c>
       <c r="C162" s="13" t="s">
@@ -11986,10 +14133,10 @@
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="22">
+      <c r="A163" s="9">
         <v>20260516</v>
       </c>
-      <c r="B163" s="26" t="s">
+      <c r="B163" s="22" t="s">
         <v>174</v>
       </c>
       <c r="C163" s="13" t="s">
@@ -12000,10 +14147,10 @@
       </c>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="22">
+      <c r="A164" s="9">
         <v>20260516</v>
       </c>
-      <c r="B164" s="26" t="s">
+      <c r="B164" s="22" t="s">
         <v>175</v>
       </c>
       <c r="C164" s="13" t="s">
@@ -12014,10 +14161,10 @@
       </c>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="22">
+      <c r="A165" s="9">
         <v>20260516</v>
       </c>
-      <c r="B165" s="26" t="s">
+      <c r="B165" s="22" t="s">
         <v>176</v>
       </c>
       <c r="C165" s="13" t="s">
@@ -12028,10 +14175,10 @@
       </c>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="22">
+      <c r="A166" s="9">
         <v>20260516</v>
       </c>
-      <c r="B166" s="26" t="s">
+      <c r="B166" s="22" t="s">
         <v>177</v>
       </c>
       <c r="C166" s="13" t="s">
@@ -12042,10 +14189,10 @@
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="22">
+      <c r="A167" s="9">
         <v>20260516</v>
       </c>
-      <c r="B167" s="26" t="s">
+      <c r="B167" s="22" t="s">
         <v>178</v>
       </c>
       <c r="C167" s="13" t="s">
@@ -12056,10 +14203,10 @@
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="22">
+      <c r="A168" s="9">
         <v>20260516</v>
       </c>
-      <c r="B168" s="26" t="s">
+      <c r="B168" s="22" t="s">
         <v>179</v>
       </c>
       <c r="C168" s="13" t="s">
@@ -12070,10 +14217,10 @@
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="22">
+      <c r="A169" s="9">
         <v>20260517</v>
       </c>
-      <c r="B169" s="24" t="s">
+      <c r="B169" s="22" t="s">
         <v>181</v>
       </c>
       <c r="C169" s="13" t="s">
@@ -12084,10 +14231,10 @@
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="22">
+      <c r="A170" s="9">
         <v>20260517</v>
       </c>
-      <c r="B170" s="24" t="s">
+      <c r="B170" s="22" t="s">
         <v>182</v>
       </c>
       <c r="C170" s="13" t="s">
@@ -12098,10 +14245,10 @@
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="22">
+      <c r="A171" s="9">
         <v>20260517</v>
       </c>
-      <c r="B171" s="24" t="s">
+      <c r="B171" s="22" t="s">
         <v>183</v>
       </c>
       <c r="C171" s="13" t="s">
@@ -12112,10 +14259,10 @@
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="22">
+      <c r="A172" s="9">
         <v>20260517</v>
       </c>
-      <c r="B172" s="24" t="s">
+      <c r="B172" s="22" t="s">
         <v>184</v>
       </c>
       <c r="C172" s="13" t="s">
@@ -12126,10 +14273,10 @@
       </c>
     </row>
     <row r="173" spans="1:4">
-      <c r="A173" s="22">
+      <c r="A173" s="9">
         <v>20260517</v>
       </c>
-      <c r="B173" s="24" t="s">
+      <c r="B173" s="22" t="s">
         <v>185</v>
       </c>
       <c r="C173" s="13" t="s">
@@ -12140,10 +14287,10 @@
       </c>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="22">
+      <c r="A174" s="9">
         <v>20260517</v>
       </c>
-      <c r="B174" s="24" t="s">
+      <c r="B174" s="22" t="s">
         <v>186</v>
       </c>
       <c r="C174" s="13" t="s">
@@ -12154,10 +14301,10 @@
       </c>
     </row>
     <row r="175" spans="1:4">
-      <c r="A175" s="22">
+      <c r="A175" s="9">
         <v>20260517</v>
       </c>
-      <c r="B175" s="24" t="s">
+      <c r="B175" s="22" t="s">
         <v>187</v>
       </c>
       <c r="C175" s="13" t="s">
@@ -12168,10 +14315,10 @@
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="22">
+      <c r="A176" s="9">
         <v>20260518</v>
       </c>
-      <c r="B176" s="26" t="s">
+      <c r="B176" s="22" t="s">
         <v>188</v>
       </c>
       <c r="C176" s="13" t="s">
@@ -12182,10 +14329,10 @@
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="22">
+      <c r="A177" s="9">
         <v>20260518</v>
       </c>
-      <c r="B177" s="26" t="s">
+      <c r="B177" s="22" t="s">
         <v>189</v>
       </c>
       <c r="C177" s="13" t="s">
@@ -12196,10 +14343,10 @@
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="22">
+      <c r="A178" s="9">
         <v>20260518</v>
       </c>
-      <c r="B178" s="26" t="s">
+      <c r="B178" s="22" t="s">
         <v>190</v>
       </c>
       <c r="C178" s="13" t="s">
@@ -12210,10 +14357,10 @@
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="22">
+      <c r="A179" s="9">
         <v>20260519</v>
       </c>
-      <c r="B179" s="26" t="s">
+      <c r="B179" s="22" t="s">
         <v>191</v>
       </c>
       <c r="C179" s="13" t="s">
@@ -12224,10 +14371,10 @@
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="22">
+      <c r="A180" s="9">
         <v>20260519</v>
       </c>
-      <c r="B180" s="26" t="s">
+      <c r="B180" s="22" t="s">
         <v>192</v>
       </c>
       <c r="C180" s="13" t="s">
@@ -12238,10 +14385,10 @@
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="22">
+      <c r="A181" s="9">
         <v>20260519</v>
       </c>
-      <c r="B181" s="24" t="s">
+      <c r="B181" s="22" t="s">
         <v>193</v>
       </c>
       <c r="C181" s="13" t="s">
@@ -12252,10 +14399,10 @@
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="22">
+      <c r="A182" s="9">
         <v>20260519</v>
       </c>
-      <c r="B182" s="26" t="s">
+      <c r="B182" s="22" t="s">
         <v>194</v>
       </c>
       <c r="C182" s="13" t="s">
@@ -12263,6 +14410,566 @@
       </c>
       <c r="D182" s="11">
         <v>878400</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="9">
+        <v>20260520</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C183" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D183" s="11">
+        <v>745200</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="9">
+        <v>20260520</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C184" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D184" s="11">
+        <v>429300</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" s="9">
+        <v>20260520</v>
+      </c>
+      <c r="B185" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="C185" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D185" s="11">
+        <v>159800</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" s="9">
+        <v>20260520</v>
+      </c>
+      <c r="B186" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="C186" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D186" s="11">
+        <v>774900</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" s="9">
+        <v>20260520</v>
+      </c>
+      <c r="B187" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="C187" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D187" s="11">
+        <v>2109240</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="9">
+        <v>20260521</v>
+      </c>
+      <c r="B188" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C188" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D188" s="11">
+        <v>472420</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="9">
+        <v>20260521</v>
+      </c>
+      <c r="B189" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C189" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D189" s="11">
+        <v>527670</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" s="9">
+        <v>20260521</v>
+      </c>
+      <c r="B190" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="C190" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D190" s="11">
+        <v>1145170</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="9">
+        <v>20260521</v>
+      </c>
+      <c r="B191" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C191" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D191" s="11">
+        <v>1436400</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" s="9">
+        <v>20260521</v>
+      </c>
+      <c r="B192" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="C192" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D192" s="11">
+        <v>3435390</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" s="9">
+        <v>20260521</v>
+      </c>
+      <c r="B193" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="C193" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D193" s="11">
+        <v>1127000</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="9">
+        <v>20260522</v>
+      </c>
+      <c r="B194" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C194" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D194" s="11">
+        <v>304200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="9">
+        <v>20260522</v>
+      </c>
+      <c r="B195" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="C195" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D195" s="11">
+        <v>95400</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="9">
+        <v>20260522</v>
+      </c>
+      <c r="B196" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C196" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D196" s="11">
+        <v>896400</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="9">
+        <v>20260522</v>
+      </c>
+      <c r="B197" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C197" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D197" s="11">
+        <v>472140</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B198" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="C198" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D198" s="5">
+        <v>1232910</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B199" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C199" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D199" s="11">
+        <v>458200</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B200" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C200" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D200" s="5">
+        <v>355500</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B201" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="C201" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D201" s="11">
+        <v>296400</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B202" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C202" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D202" s="11">
+        <v>194700</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B203" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="C203" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D203" s="5">
+        <v>141600</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B204" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="C204" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D204" s="5">
+        <v>1144600</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="9">
+        <v>20260523</v>
+      </c>
+      <c r="B205" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C205" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D205" s="11">
+        <v>188100</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="9">
+        <v>20260524</v>
+      </c>
+      <c r="B206" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C206" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D206" s="11">
+        <v>395000</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="9">
+        <v>20260524</v>
+      </c>
+      <c r="B207" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C207" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D207" s="11">
+        <v>141600</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="9">
+        <v>20260524</v>
+      </c>
+      <c r="B208" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C208" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D208" s="11">
+        <v>331800</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="9">
+        <v>20260524</v>
+      </c>
+      <c r="B209" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C209" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D209" s="11">
+        <v>244900</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="9">
+        <v>20260524</v>
+      </c>
+      <c r="B210" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="C210" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D210" s="11">
+        <v>210700</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="9">
+        <v>20260524</v>
+      </c>
+      <c r="B211" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C211" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D211" s="5">
+        <v>224200</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="9">
+        <v>20260524</v>
+      </c>
+      <c r="B212" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C212" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D212" s="11">
+        <v>220660</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="9">
+        <v>20260525</v>
+      </c>
+      <c r="B213" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C213" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D213" s="5">
+        <v>316000</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="9">
+        <v>20260525</v>
+      </c>
+      <c r="B214" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C214" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D214" s="5">
+        <v>480340</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="9">
+        <v>20260525</v>
+      </c>
+      <c r="B215" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C215" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D215" s="5">
+        <v>121500</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="9">
+        <v>20260525</v>
+      </c>
+      <c r="B216" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C216" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D216" s="5">
+        <v>395890</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="9">
+        <v>20260525</v>
+      </c>
+      <c r="B217" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="C217" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D217" s="11">
+        <v>1313400</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="9">
+        <v>20260526</v>
+      </c>
+      <c r="B218" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C218" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D218" s="11">
+        <v>418900</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="9">
+        <v>20260526</v>
+      </c>
+      <c r="B219" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C219" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D219" s="5">
+        <v>323900</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="9">
+        <v>20260526</v>
+      </c>
+      <c r="B220" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C220" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D220" s="5">
+        <v>524300</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="9">
+        <v>20260526</v>
+      </c>
+      <c r="B221" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C221" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D221" s="5">
+        <v>892500</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="9">
+        <v>20260526</v>
+      </c>
+      <c r="B222" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C222" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D222" s="5">
+        <v>343000</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sodomall-my.sharepoint.com/personal/jinyeong617_sodomall_com/Documents/당근/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{9D1964EF-D87C-40DB-87AD-82C7614BA687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D255B4FD-CFCC-4DB6-89E4-6549BDF8CE15}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{9D1964EF-D87C-40DB-87AD-82C7614BA687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4344E010-637A-4C26-A554-C83463F031CC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77D1A517-C785-428C-9931-F09A076C124D}"/>
+    <workbookView xWindow="29850" yWindow="1545" windowWidth="23745" windowHeight="14730" xr2:uid="{77D1A517-C785-428C-9931-F09A076C124D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="295">
   <si>
     <t>상품</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -11200,6 +11200,2262 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 150g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국내산 양념편육 1팩 (300g)</t>
+  </si>
+  <si>
+    <t>오장동 '물'냉면 1인분</t>
+  </si>
+  <si>
+    <t>오장동 '비빔'냉면 1인분</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀빈정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열무김치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1kg)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>십이지신 썸머패치 1개 (48매입)</t>
+  </si>
+  <si>
+    <t>부처스나인 직화스테이크 1개(160g)</t>
+  </si>
+  <si>
+    <t>에코프랜 스텐도마 'ㄱ'자형 1개(중형)</t>
+  </si>
+  <si>
+    <t>마법 수세미 1세트 (10개입)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삼진어묵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어묵탕용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종합모듬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2kg)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참크래커 알프스 1곽(295g/15개입)</t>
+  </si>
+  <si>
+    <t>'김치' 큐브치즈 1팩(36g/8개입)</t>
+  </si>
+  <si>
+    <t>'김' 큐브치즈 1팩(36g/8개입)</t>
+  </si>
+  <si>
+    <t>'와사비' 큐브치즈 1팩(36g/8개입)</t>
+  </si>
+  <si>
+    <t>탁상용 서큘레이터 1개 (색상랜덤)</t>
+  </si>
+  <si>
+    <t>국가대표 명태회무침 1개 (400g)</t>
+  </si>
+  <si>
+    <t>루솔 진한 배도라지즙 1박스</t>
+  </si>
+  <si>
+    <t>뉴라덤 코어타임 앰플 1세트(2개)</t>
+  </si>
+  <si>
+    <t>코오롱제약 프레쉬 구강유산균 (30정)</t>
+  </si>
+  <si>
+    <t>눈건강엔 루테인 (30캡슐)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리쌀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어포튀각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오리지널</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (15g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메밀소바</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>육수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매콤 오리주물럭 1팩 (500g)</t>
+  </si>
+  <si>
+    <t>[235] 테디 아일랜드 EVA 슬리퍼</t>
+  </si>
+  <si>
+    <t>[245] 테디 아일랜드 EVA 슬리퍼</t>
+  </si>
+  <si>
+    <t>[255] 테디 아일랜드 EVA 슬리퍼</t>
+  </si>
+  <si>
+    <t>버블 마스크 [브라운] 1병 (95ml)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모기기피제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ''</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물지마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>''(60ml)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비네이쳐스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아누카리치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탈모샴푸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 480ml</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스프린트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자몽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이온음료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>500ml</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>박스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스프린트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자몽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이온음료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리땅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양배추즙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>*90ml</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청룡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순대국밥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (200g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청룡 얼큰 순대국밥 1팩 (200g)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이츠웰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>애플망고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1kg)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단호박</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>박스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (50g*20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교동 추어탕 1팩 (450g)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>릴렉시즘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더바르게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교정브라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>/S)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀빈정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생콩국수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>트러플크림치킨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피타브레드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>토마토바질</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피타브레드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>콘치즈에그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피타브레드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깔끔이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈썹정리칼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>*2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마이코튼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세탁시트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마하차녹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>망고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5kg(10~12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내외</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시린메드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에프치약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 125g</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시린메드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에프치약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 125g</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납작당면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국물닭발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (600g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국내산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매콤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오돌뼈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(300g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냉동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소불고기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유부초밥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (360g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비타민</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>C 2000 (30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국내산 팽이버섯 3봉*약 150g</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>염장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미역줄기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 250g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국내산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>염장 다시마 (약 250g)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국내산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부추</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 500g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시래기 뼈해장국 1팩 (900g)</t>
+  </si>
+  <si>
+    <t>아침 샌드위치 식빵 1봉 (790g)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다파니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅콩버터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>크리미</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (340g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다파니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅콩버터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>크런치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (340g)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영진약품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로메디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생유산균</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2A3038"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곽</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -11208,7 +13464,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11379,6 +13635,19 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A3038"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A3038"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -11447,7 +13716,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11529,6 +13798,12 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -11555,6 +13830,14 @@
 </file>
 
 <file path=xl/persons/person1.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person2.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person3.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -11855,7 +14138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC37B53-3382-4F2F-9306-BB57C25FEA41}">
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:D284"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.375" customWidth="1"/>
@@ -14972,6 +17255,874 @@
         <v>343000</v>
       </c>
     </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="9">
+        <v>20260527</v>
+      </c>
+      <c r="B223" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C223" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D223" s="11">
+        <v>524400</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="9">
+        <v>20260527</v>
+      </c>
+      <c r="B224" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C224" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D224" s="11">
+        <v>1175610</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="9">
+        <v>20260527</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="C225" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D225" s="11">
+        <v>974460</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="9">
+        <v>20260527</v>
+      </c>
+      <c r="B226" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="C226" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D226" s="11">
+        <v>513500</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="9">
+        <v>20260527</v>
+      </c>
+      <c r="B227" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="C227" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D227" s="11">
+        <v>344310</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="9">
+        <v>20260527</v>
+      </c>
+      <c r="B228" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C228" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D228" s="11">
+        <v>608650</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="9">
+        <v>20260527</v>
+      </c>
+      <c r="B229" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C229" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D229" s="11">
+        <v>279200</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B230" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C230" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D230" s="11">
+        <v>480600</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B231" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C231" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D231" s="11">
+        <v>316800</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B232" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C232" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D232" s="11">
+        <v>1290500</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B233" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C233" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D233" s="11">
+        <v>404550</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B234" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C234" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D234" s="11">
+        <v>43890</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B235" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="C235" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D235" s="11">
+        <v>35910</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B236" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C236" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D236" s="11">
+        <v>55860</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="9">
+        <v>20260528</v>
+      </c>
+      <c r="B237" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C237" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D237" s="11">
+        <v>1059300</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="9">
+        <v>20260529</v>
+      </c>
+      <c r="B238" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C238" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D238" s="11">
+        <v>608300</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="9">
+        <v>20260529</v>
+      </c>
+      <c r="B239" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C239" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D239" s="11">
+        <v>397500</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="9">
+        <v>20260529</v>
+      </c>
+      <c r="B240" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C240" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D240" s="11">
+        <v>199000</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="9">
+        <v>20260529</v>
+      </c>
+      <c r="B241" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C241" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D241" s="11">
+        <v>719800</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="9">
+        <v>20260529</v>
+      </c>
+      <c r="B242" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C242" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D242" s="11">
+        <v>1228500</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="9">
+        <v>20260530</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C243" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D243" s="11">
+        <v>340560</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="9">
+        <v>20260530</v>
+      </c>
+      <c r="B244" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="C244" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D244" s="11">
+        <v>579090</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="9">
+        <v>20260530</v>
+      </c>
+      <c r="B245" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C245" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D245" s="11">
+        <v>929670</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="9">
+        <v>20260530</v>
+      </c>
+      <c r="B246" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C246" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D246" s="11">
+        <v>59400</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="9">
+        <v>20260530</v>
+      </c>
+      <c r="B247" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C247" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D247" s="11">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="9">
+        <v>20260530</v>
+      </c>
+      <c r="B248" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C248" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D248" s="11">
+        <v>39600</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="9">
+        <v>20260530</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C249" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D249" s="11">
+        <v>569400</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B250" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C250" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D250" s="11">
+        <v>269700</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B251" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C251" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D251" s="11">
+        <v>269700</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B252" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C252" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D252" s="11">
+        <v>351900</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B253" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C253" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D253" s="11">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B254" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C254" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D254" s="11">
+        <v>648000</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C255" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D255" s="11">
+        <v>180600</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B256" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C256" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D256" s="11">
+        <v>550160</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B257" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C257" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D257" s="11">
+        <v>373750</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B258" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C258" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D258" s="11">
+        <v>762090</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="9">
+        <v>20260531</v>
+      </c>
+      <c r="B259" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C259" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D259" s="5">
+        <v>227700</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="9">
+        <v>20260601</v>
+      </c>
+      <c r="B260" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C260" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D260" s="5">
+        <v>999000</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="9">
+        <v>20260601</v>
+      </c>
+      <c r="B261" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C261" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D261" s="11">
+        <v>259700</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="9">
+        <v>20260601</v>
+      </c>
+      <c r="B262" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C262" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D262" s="11">
+        <v>783020</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="9">
+        <v>20260602</v>
+      </c>
+      <c r="B263" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C263" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D263" s="5">
+        <v>524700</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="9">
+        <v>20260602</v>
+      </c>
+      <c r="B264" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C264" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D264" s="11">
+        <v>702900</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="9">
+        <v>20260602</v>
+      </c>
+      <c r="B265" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C265" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D265" s="11">
+        <v>425700</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="9">
+        <v>20260602</v>
+      </c>
+      <c r="B266" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C266" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D266" s="5">
+        <v>104400</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="9">
+        <v>20260602</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C267" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D267" s="5">
+        <v>186200</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="9">
+        <v>20260602</v>
+      </c>
+      <c r="B268" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C268" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D268" s="5">
+        <v>957600</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B269" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C269" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D269" s="11">
+        <v>40500</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B270" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C270" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D270" s="5">
+        <v>430920</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B271" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C271" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D271" s="5">
+        <v>359550</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B272" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C272" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D272" s="11">
+        <v>254490</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C273" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D273" s="11">
+        <v>185690</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B274" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C274" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D274" s="11">
+        <v>409180</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B275" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C275" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D275" s="5">
+        <v>89000</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B276" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C276" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D276" s="11">
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B277" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="C277" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D277" s="5">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B278" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="C278" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D278" s="11">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="9">
+        <v>20260603</v>
+      </c>
+      <c r="B279" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C279" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D279" s="5">
+        <v>157000</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="9">
+        <v>20260604</v>
+      </c>
+      <c r="B280" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C280" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D280" s="5">
+        <v>977220</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="9">
+        <v>20260604</v>
+      </c>
+      <c r="B281" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="C281" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D281" s="5">
+        <v>367770</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="9">
+        <v>20260604</v>
+      </c>
+      <c r="B282" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C282" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D282" s="5">
+        <v>726570</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="9">
+        <v>20260604</v>
+      </c>
+      <c r="B283" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C283" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D283" s="5">
+        <v>654810</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="9">
+        <v>20260604</v>
+      </c>
+      <c r="B284" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C284" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D284" s="5">
+        <v>507400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
